--- a/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -570,22 +570,10 @@
     <t>79267</t>
   </si>
   <si>
-    <t>MSG_INTERNAL_ERROR</t>
-  </si>
-  <si>
-    <t>79268</t>
-  </si>
-  <si>
     <t>MSG_PARAM_UNKNOWN</t>
   </si>
   <si>
     <t>79269</t>
-  </si>
-  <si>
-    <t>MSG_TIMEOUT</t>
-  </si>
-  <si>
-    <t>79270</t>
   </si>
   <si>
     <t>MSG_UNKNOWN_OPERATION</t>
@@ -1973,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2127,32 +2115,6 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -96,6 +96,9 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>gematik GmbH / Dieser Implementation Guide ist lizenziert unter [Apache License](./license.html), Version 2.0.</t>
+  </si>
+  <si>
     <t>Source</t>
   </si>
   <si>
@@ -376,6 +379,18 @@
   </si>
   <si>
     <t>79275</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FEATURE</t>
+  </si>
+  <si>
+    <t>79268</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FLOWTYPE</t>
+  </si>
+  <si>
+    <t>79270</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-chargeitem-operation-outcome-details-cs</t>
@@ -830,7 +845,9 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -839,601 +856,627 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E47" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1447,100 +1490,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1556,74 +1599,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1639,139 +1682,139 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1787,74 +1830,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1870,87 +1913,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1966,152 +2009,152 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E11" s="2"/>
     </row>

--- a/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -13,13 +13,12 @@
     <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
     <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
     <sheet name="Mapping Table 5" r:id="rId9" sheetId="7"/>
-    <sheet name="Mapping Table 6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -426,76 +425,73 @@
     <t>79243</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-xborder-operation-outcome-details-cs</t>
-  </si>
-  <si>
-    <t>TIFLOW_XBORDER_COUNTRY_CODE_INVALID</t>
+    <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-erezept-operation-outcome-details-cs</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_DRUG_CATEGORY_FORBIDDEN</t>
+  </si>
+  <si>
+    <t>79247</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_ENDDATE_INVALID</t>
+  </si>
+  <si>
+    <t>79248</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_FLOWTYPE_INVALID</t>
+  </si>
+  <si>
+    <t>79249</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_ID_INVALID</t>
+  </si>
+  <si>
+    <t>79250</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_INVALID</t>
+  </si>
+  <si>
+    <t>79251</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_NOT_VALID</t>
+  </si>
+  <si>
+    <t>79252</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_MVO_STARTDATE_INVALID</t>
+  </si>
+  <si>
+    <t>79253</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_PZN_INVALID</t>
+  </si>
+  <si>
+    <t>79254</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_COUNTRY_CODE_INVALID</t>
   </si>
   <si>
     <t>79244</t>
   </si>
   <si>
-    <t>TIFLOW_XBORDER_NOT_ACTIVATED</t>
+    <t>TIFLOW_EREZEPT_NOT_ACTIVATED</t>
   </si>
   <si>
     <t>79245</t>
   </si>
   <si>
-    <t>TIFLOW_XBORDER_NO_PRESCRIPTIONS_FOUND</t>
+    <t>TIFLOW_EREZEPT_NO_PRESCRIPTIONS_FOUND</t>
   </si>
   <si>
     <t>79246</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-erezept-operation-outcome-details-cs</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_DRUG_CATEGORY_FORBIDDEN</t>
-  </si>
-  <si>
-    <t>79247</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_ENDDATE_INVALID</t>
-  </si>
-  <si>
-    <t>79248</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_FLOWTYPE_INVALID</t>
-  </si>
-  <si>
-    <t>79249</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_ID_INVALID</t>
-  </si>
-  <si>
-    <t>79250</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_INVALID</t>
-  </si>
-  <si>
-    <t>79251</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_NOT_VALID</t>
-  </si>
-  <si>
-    <t>79252</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_MVO_STARTDATE_INVALID</t>
-  </si>
-  <si>
-    <t>79253</t>
-  </si>
-  <si>
-    <t>TIFLOW_EREZEPT_PZN_INVALID</t>
-  </si>
-  <si>
-    <t>79254</t>
   </si>
   <si>
     <t>json-fehlercodes</t>
@@ -1594,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1669,6 +1665,110 @@
         <v>141</v>
       </c>
       <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1677,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1699,7 +1799,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1716,107 +1816,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1825,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1847,7 +1882,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1864,42 +1899,55 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1908,102 +1956,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -2026,7 +1978,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2043,118 +1995,118 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E11" s="2"/>
     </row>
